--- a/output/pdf_financials_xlsx/BAG.xlsx
+++ b/output/pdf_financials_xlsx/BAG.xlsx
@@ -5446,43 +5446,43 @@
         <v>2.889494</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.889494</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.889494</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.889494</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.889494</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.889494</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.032994</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.120537</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.135537</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.401224</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.432221</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.432221</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.432221</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.432221</v>
       </c>
     </row>
     <row r="93">
@@ -6771,37 +6771,37 @@
         <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.010652</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0024</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.717262</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.168472</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.256555</v>
+        <v>0.220745</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-1.265654</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.201518</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>0.001191</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.01295</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000404</v>
       </c>
     </row>
     <row r="119">
@@ -8952,7 +8952,11 @@
           <t>Share based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -9577,7 +9581,11 @@
           <t>Share based payment reserve (Notes 6 and 7)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -10028,7 +10036,11 @@
           <t>Share based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -10708,7 +10720,11 @@
           <t>Share based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -11157,7 +11173,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -12959,7 +12979,11 @@
           <t>Share based payment reserve</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="n">
         <v>2.82994</v>
       </c>
@@ -15807,7 +15831,11 @@
           <t>Exploration and evaluation asset expenditures, net</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -18621,7 +18649,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BAG.xlsx
+++ b/output/pdf_financials_xlsx/BAG.xlsx
@@ -978,10 +978,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.033936</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006997</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1908,10 +1908,10 @@
         <v>-2.137648</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.934672</v>
+        <v>-1.968608</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.846766</v>
+        <v>-0.853763</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-9.490093999999999</v>
@@ -2012,10 +2012,10 @@
         <v>-2.137648</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.903516</v>
+        <v>-1.937452</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.801393</v>
+        <v>-0.8083900000000001</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-9.456849</v>
@@ -2284,49 +2284,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>4.314916</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.459942</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.08755300000000001</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002351</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000239</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.002155</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000445</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.026203</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000293</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000215</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.40956</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.09973799999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.00011</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.00228</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.000799</v>
       </c>
     </row>
     <row r="35">
@@ -2388,49 +2388,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>4.314916</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.459942</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.08755300000000001</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002351</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000239</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.002155</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000445</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.026203</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000293</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000215</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.40956</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.09973799999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.00011</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.00228</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.000799</v>
       </c>
     </row>
     <row r="37">
@@ -3012,49 +3012,49 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.34279</v>
+        <v>0.027874</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.507534</v>
+        <v>0.047592</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.096928</v>
+        <v>0.009375</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.002351</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.000239</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.002155</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.000445</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.102535</v>
+        <v>0.076332</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.021609</v>
+        <v>0.021316</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.010214</v>
+        <v>0.009998999999999999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.504614</v>
+        <v>0.095054</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.128118</v>
+        <v>0.02838</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.012037</v>
+        <v>0.011927</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.01127</v>
+        <v>0.00899</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.012603</v>
+        <v>0.011804</v>
       </c>
     </row>
     <row r="49">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
@@ -34906,7 +34906,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">

--- a/output/pdf_financials_xlsx/BAG.xlsx
+++ b/output/pdf_financials_xlsx/BAG.xlsx
@@ -6343,16 +6343,16 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.008943</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.008036</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.00699</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.007998999999999999</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -6395,10 +6395,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012568</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.170735</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012568</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.170735</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -21531,7 +21531,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -23333,7 +23337,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E176" s="5" t="n">
         <v>-0.012568</v>
       </c>
@@ -23511,7 +23519,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -24334,7 +24346,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E187" s="5" t="n">
         <v>0.008943</v>
       </c>
